--- a/剧情配置/事件与节点配置表.xlsx
+++ b/剧情配置/事件与节点配置表.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="58">
   <si>
     <t>中文名</t>
   </si>
@@ -163,15 +163,6 @@
   </si>
   <si>
     <t>权重</t>
-  </si>
-  <si>
-    <t>条件JSON</t>
-  </si>
-  <si>
-    <t>消耗JSON</t>
-  </si>
-  <si>
-    <t>效果JSON</t>
   </si>
   <si>
     <t>目标中文名</t>
@@ -890,13 +881,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="10" width="13" customWidth="1"/>
+    <col min="1" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -918,28 +909,19 @@
       <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>25</v>
@@ -948,30 +930,21 @@
         <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
         <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>25</v>
@@ -980,19 +953,10 @@
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1000,10 +964,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>25</v>
@@ -1012,30 +976,21 @@
         <v>6</v>
       </c>
       <c r="G4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
@@ -1044,30 +999,21 @@
         <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>25</v>
@@ -1076,30 +1022,21 @@
         <v>6</v>
       </c>
       <c r="G6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
@@ -1108,30 +1045,21 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
@@ -1140,15 +1068,6 @@
         <v>6</v>
       </c>
       <c r="G8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" t="s">
         <v>21</v>
       </c>
     </row>

--- a/剧情配置/事件与节点配置表.xlsx
+++ b/剧情配置/事件与节点配置表.xlsx
@@ -3,17 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="15400" activeTab="1"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="事件" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="剧情节点" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="按钮" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="校验" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
   <si>
     <t>中文名</t>
   </si>
@@ -30,28 +34,31 @@
     <t>配图(中文名)</t>
   </si>
   <si>
-    <t>初入青云</t>
+    <t>婴儿期事件一</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>婴幼儿</t>
+  </si>
+  <si>
+    <t>测试1</t>
+  </si>
+  <si>
+    <t>/cg/清纯/平儿.jpg</t>
+  </si>
+  <si>
+    <t>遭遇强敌</t>
+  </si>
+  <si>
+    <t>nb_002</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>青云篇</t>
-  </si>
-  <si>
-    <t>主角初到青云宗外门</t>
-  </si>
-  <si>
-    <t>平儿.jpg</t>
-  </si>
-  <si>
-    <t>青云内门</t>
-  </si>
-  <si>
-    <t>入门后内门修行</t>
-  </si>
-  <si>
-    <t>袭人.jpg</t>
+    <t>/cg/清纯/袭人.jpg</t>
   </si>
   <si>
     <t>节点ID</t>
@@ -78,73 +85,54 @@
     <t>通过后开商店</t>
   </si>
   <si>
-    <t>山门之前</t>
-  </si>
-  <si>
-    <t>你立于青云宗山门前，云雾缭绕。</t>
-  </si>
-  <si>
-    <t>节点一背景.jpg</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>n001</t>
+  </si>
+  <si>
+    <t>童年1</t>
+  </si>
+  <si>
+    <t>穿越到来</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这一天，我正挤着地铁朝公司走，忽然脚下一滑，失去了意识，再睁眼的时候，已经到了一个修仙的世界。
+为首一人，仙风道骨，白眉齐胸。旁边一人满脸献媚状：师尊，我看此人筋骨上佳。不如收入我门……拿去炼丹！</t>
+  </si>
+  <si>
+    <t>/node/节点一背景.jpg</t>
   </si>
   <si>
     <t>否</t>
   </si>
   <si>
-    <t>叩门</t>
-  </si>
-  <si>
-    <t>叩响山门</t>
-  </si>
-  <si>
-    <t>你叩响山门。</t>
-  </si>
-  <si>
-    <t>节点二背景.jpg</t>
-  </si>
-  <si>
-    <t>观望</t>
-  </si>
-  <si>
-    <t>暗中观察</t>
-  </si>
-  <si>
-    <t>你暗中观察四周。</t>
-  </si>
-  <si>
-    <t>节点三背景.jpg</t>
-  </si>
-  <si>
-    <t>正厅</t>
-  </si>
-  <si>
-    <t>正厅相遇</t>
-  </si>
-  <si>
-    <t>东厢与西厢在此汇聚——但编号只看声明的父。</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>内门入口</t>
-  </si>
-  <si>
-    <t>你踏入内门。</t>
-  </si>
-  <si>
-    <t>节点五背景.jpg</t>
-  </si>
-  <si>
-    <t>内门深处</t>
-  </si>
-  <si>
-    <t>内门幽深。</t>
-  </si>
-  <si>
-    <t>节点六背景.jpg</t>
+    <t>n002</t>
+  </si>
+  <si>
+    <t>事件2</t>
+  </si>
+  <si>
+    <t>脱困</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你的枪尖指向对面，身上红绫飘动。那名白须齐胸的道长，满脸阴云。
+你向地下的两具尸体扫了一眼：“小爷前世有个外号，叫三太子……”</t>
+  </si>
+  <si>
+    <t>/node/节点二背景.jpg</t>
+  </si>
+  <si>
+    <t>n003</t>
+  </si>
+  <si>
+    <t>强敌</t>
+  </si>
+  <si>
+    <t>虚空怪兽</t>
+  </si>
+  <si>
+    <t>长眉道长的身后，一个青面獠牙的硕大黑影扭动着。他冷哼了一声：主角死于话多！……</t>
+  </si>
+  <si>
+    <t>/node/节点三背景.jpg</t>
   </si>
   <si>
     <t>关联节点中文名</t>
@@ -168,32 +156,41 @@
     <t>目标中文名</t>
   </si>
   <si>
-    <t>1</t>
+    <t>睡懒觉</t>
   </si>
   <si>
     <t>normal</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>转身离去</t>
-  </si>
-  <si>
-    <t>前往正厅</t>
-  </si>
-  <si>
-    <t>深入内门</t>
-  </si>
-  <si>
-    <t>回山门</t>
+    <t>是</t>
+  </si>
+  <si>
+    <t>与他心平气和地讲讲道理</t>
+  </si>
+  <si>
+    <t>级别</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>单元格</t>
+  </si>
+  <si>
+    <t>信息</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>全部校验通过，可同步数据库</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -203,14 +200,28 @@
     </font>
     <font>
       <b/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1C1B18"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E0D0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -230,9 +241,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -327,7 +341,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -362,7 +375,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -397,16 +409,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -528,56 +544,16 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="4" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
-    <col min="1" max="5" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16.3461538461538" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -619,74 +595,74 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="10" width="13" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="7" max="7" width="30.7692307692308" customWidth="1"/>
+    <col min="8" max="8" width="11.7307692307692" customWidth="1"/>
+    <col min="9" max="9" width="9.42307692307692" customWidth="1"/>
+    <col min="10" max="10" width="13.8461538461538" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -695,380 +671,209 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
+        <v>37</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="7" width="13" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="6" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
+        <v>47</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>53</v>
       </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>54</v>
-      </c>
-      <c r="D4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
